--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -413,9 +413,580 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>torque 1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>torque 2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>torque 3</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>torque 4</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>torque 5</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>torque 6</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>angle 1</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>angle 2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>angle 3</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>angle 4</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>angle 5</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>angle 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.97215226305253e-31</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-12.07575267498073</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.176107834607471</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0008560691557944302</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-9.575743663520994e-19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>-2.958228394578794e-31</v>
+      </c>
+      <c r="B3" t="n">
+        <v>14.22223425295025</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.322589412576989</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0008560691557944302</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-9.575743663520994e-19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-9.860761315262648e-32</v>
+      </c>
+      <c r="B4" t="n">
+        <v>14.42433641696221</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.524691576588942</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2029582331677464</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.007819188087690263</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>180</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-14.42433641696221</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-3.524691576588942</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.2029582331677464</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.007819188087690263</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-7.374953263784322</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.524691576588942</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2029582331677464</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.007819188087690263</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-14.42433641696221</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-3.524691576588942</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2029582331677464</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.007819188087690263</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>-9.860761315262648e-32</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-14.01841995062671</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-3.118775110253449</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2029582331677464</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.007819188087690263</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>90</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-14.42433641696221</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-3.524691576588942</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2029582331677464</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.007819188087690263</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-9.860761315262648e-32</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-14.01841995062671</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-3.118775110253449</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2029582331677464</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.007819188087690263</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>90</v>
+      </c>
+      <c r="K10" t="n">
+        <v>180</v>
+      </c>
+      <c r="L10" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-9.860761315262648e-32</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-14.01841995062671</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-3.118775110253449</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2029582331677464</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.007819188087690263</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>90</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Torque 1 max</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Torque 2 max</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Torque 3 max</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Torque 4 max</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Torque 5 max</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Torque 6 max</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.97215226305253e-31</v>
+      </c>
+      <c r="B15" t="n">
+        <v>14.42433641696221</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.524691576588942</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2029582331677464</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.007819188087690263</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -480,19 +480,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.97215226305253e-31</v>
+        <v>37.29342666571565</v>
       </c>
       <c r="B2" t="n">
-        <v>-12.07575267498073</v>
+        <v>5.5128518508504</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.176107834607471</v>
+        <v>4.787450787944128</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008560691557944302</v>
+        <v>1.05165401696865</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.575743663520994e-19</v>
+        <v>-0.08677603686829725</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -504,13 +504,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L2" t="n">
         <v>90</v>
@@ -518,19 +518,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-2.958228394578794e-31</v>
+        <v>-8.303409606740855</v>
       </c>
       <c r="B3" t="n">
-        <v>14.22223425295025</v>
+        <v>51.2415297628493</v>
       </c>
       <c r="C3" t="n">
-        <v>3.322589412576989</v>
+        <v>24.41884567424637</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008560691557944302</v>
+        <v>4.049186140478723</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.575743663520994e-19</v>
+        <v>-0.3365898108096151</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -551,24 +551,24 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>31.7566658472833</v>
       </c>
       <c r="B4" t="n">
-        <v>14.42433641696221</v>
+        <v>100.8222223966858</v>
       </c>
       <c r="C4" t="n">
-        <v>3.524691576588942</v>
+        <v>50.24288233764403</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.1573224323349</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.007819188087690263</v>
+        <v>0.3005437312319756</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
         <v>-90</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L4" t="n">
         <v>90</v>
@@ -594,19 +594,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>22.65501523052485</v>
       </c>
       <c r="B5" t="n">
-        <v>-14.42433641696221</v>
+        <v>-12.09011002367678</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.524691576588942</v>
+        <v>-3.407073116842879</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2029582331677464</v>
+        <v>1.71806326897798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007819188087690263</v>
+        <v>-0.1957279670014678</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K5" t="n">
         <v>-90</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>90</v>
@@ -632,19 +632,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>30.98547397206026</v>
       </c>
       <c r="B6" t="n">
-        <v>-7.374953263784322</v>
+        <v>100.6584823600145</v>
       </c>
       <c r="C6" t="n">
-        <v>3.524691576588942</v>
+        <v>50.26615240217648</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.35671992755688</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.007819188087690263</v>
+        <v>0.8630218609018455</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -653,10 +653,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I6" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>-90</v>
@@ -670,19 +670,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>5.501395728711228</v>
       </c>
       <c r="B7" t="n">
-        <v>-14.42433641696221</v>
+        <v>12.15106318491549</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.524691576588942</v>
+        <v>-12.58585838283085</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2029582331677464</v>
+        <v>2.770297592144732</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.2306389528348414</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -691,36 +691,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J7" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L7" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>30.15256250125</v>
       </c>
       <c r="B8" t="n">
-        <v>-14.01841995062671</v>
+        <v>99.9423108614517</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.118775110253449</v>
+        <v>49.99368851211411</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.50214298883856</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.007819188087690263</v>
+        <v>-0.2845330113819173</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -729,36 +729,36 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L8" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>21.34985423081358</v>
       </c>
       <c r="B9" t="n">
-        <v>-14.42433641696221</v>
+        <v>64.82164830207921</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.524691576588942</v>
+        <v>23.46373611157386</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2029582331677464</v>
+        <v>-7.937018067628466</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007819188087690263</v>
+        <v>-0.2252307533134655</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -767,16 +767,16 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9" t="n">
         <v>90</v>
@@ -784,19 +784,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>30.98547397206026</v>
       </c>
       <c r="B10" t="n">
-        <v>-14.01841995062671</v>
+        <v>100.6584823600145</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.118775110253449</v>
+        <v>50.26615240217648</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.35671992755688</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.8630218609018455</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K10" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>90</v>
@@ -822,19 +822,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>30.93977386632092</v>
       </c>
       <c r="B11" t="n">
-        <v>-14.01841995062671</v>
+        <v>100.0898807917456</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.118775110253449</v>
+        <v>49.95424834120423</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.28657538723914</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007819188087690263</v>
+        <v>-0.8565713265241622</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -843,16 +843,16 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L11" t="n">
         <v>90</v>
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.97215226305253e-31</v>
+        <v>37.29342666571565</v>
       </c>
       <c r="B15" t="n">
-        <v>14.42433641696221</v>
+        <v>100.8222223966858</v>
       </c>
       <c r="C15" t="n">
-        <v>3.524691576588942</v>
+        <v>50.26615240217648</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.50214298883856</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.8630218609018455</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -480,19 +480,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>37.29342666571565</v>
+        <v>2.958228394578794e-31</v>
       </c>
       <c r="B2" t="n">
-        <v>5.5128518508504</v>
+        <v>7.522114441330482</v>
       </c>
       <c r="C2" t="n">
-        <v>4.787450787944128</v>
+        <v>-1.180750279458152</v>
       </c>
       <c r="D2" t="n">
-        <v>1.05165401696865</v>
+        <v>3.632467677344708e-11</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.08677603686829725</v>
+        <v>1.96756785250306e-18</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -501,10 +501,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="J2" t="n">
         <v>-90</v>
@@ -518,19 +518,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-8.303409606740855</v>
+        <v>-2.465190328815662e-31</v>
       </c>
       <c r="B3" t="n">
-        <v>51.2415297628493</v>
+        <v>5.962385599298388</v>
       </c>
       <c r="C3" t="n">
-        <v>24.41884567424637</v>
+        <v>-2.740479121490243</v>
       </c>
       <c r="D3" t="n">
-        <v>4.049186140478723</v>
+        <v>0.008247222647425225</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3365898108096151</v>
+        <v>1.57257359396585e-19</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -539,36 +539,36 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="I3" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>31.7566658472833</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>100.8222223966858</v>
+        <v>11.65454929809405</v>
       </c>
       <c r="C4" t="n">
-        <v>50.24288233764403</v>
+        <v>2.951684577305415</v>
       </c>
       <c r="D4" t="n">
-        <v>10.1573224323349</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3005437312319756</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>180</v>
+        <v>-180</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
         <v>-90</v>
       </c>
       <c r="K4" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>90</v>
@@ -594,19 +594,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22.65501523052485</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-12.09011002367678</v>
+        <v>-11.65454929809405</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.407073116842879</v>
+        <v>-2.951684577305415</v>
       </c>
       <c r="D5" t="n">
-        <v>1.71806326897798</v>
+        <v>-0.2029582331677464</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1957279670014678</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K5" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>90</v>
@@ -632,19 +632,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30.98547397206026</v>
+        <v>-4.930380657631324e-32</v>
       </c>
       <c r="B6" t="n">
-        <v>100.6584823600145</v>
+        <v>-5.751180143483218</v>
       </c>
       <c r="C6" t="n">
-        <v>50.26615240217648</v>
+        <v>2.951684577305415</v>
       </c>
       <c r="D6" t="n">
-        <v>10.35671992755688</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8630218609018455</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -653,10 +653,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="J6" t="n">
         <v>-90</v>
@@ -670,19 +670,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5.501395728711228</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>12.15106318491549</v>
+        <v>-11.65454929809405</v>
       </c>
       <c r="C7" t="n">
-        <v>-12.58585838283085</v>
+        <v>-2.951684577305415</v>
       </c>
       <c r="D7" t="n">
-        <v>2.770297592144732</v>
+        <v>-0.2029582331677464</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2306389528348414</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -691,36 +691,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="K7" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30.15256250125</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B8" t="n">
-        <v>99.9423108614517</v>
+        <v>-11.24863283175856</v>
       </c>
       <c r="C8" t="n">
-        <v>49.99368851211411</v>
+        <v>-2.545768110969922</v>
       </c>
       <c r="D8" t="n">
-        <v>10.50214298883856</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2845330113819173</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -729,36 +729,36 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21.34985423081358</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>64.82164830207921</v>
+        <v>-11.65454929809405</v>
       </c>
       <c r="C9" t="n">
-        <v>23.46373611157386</v>
+        <v>-2.951684577305415</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.937018067628466</v>
+        <v>-0.2029582331677464</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2252307533134655</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -767,16 +767,16 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K9" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>90</v>
@@ -784,19 +784,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30.98547397206026</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B10" t="n">
-        <v>100.6584823600145</v>
+        <v>-11.24863283175856</v>
       </c>
       <c r="C10" t="n">
-        <v>50.26615240217648</v>
+        <v>-2.545768110969922</v>
       </c>
       <c r="D10" t="n">
-        <v>10.35671992755688</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8630218609018455</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>90</v>
+      </c>
+      <c r="K10" t="n">
         <v>180</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-90</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>90</v>
@@ -822,19 +822,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30.93977386632092</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B11" t="n">
-        <v>100.0898807917456</v>
+        <v>-11.24863283175856</v>
       </c>
       <c r="C11" t="n">
-        <v>49.95424834120423</v>
+        <v>-2.545768110969922</v>
       </c>
       <c r="D11" t="n">
-        <v>10.28657538723914</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8565713265241622</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -843,16 +843,16 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>90</v>
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37.29342666571565</v>
+        <v>2.958228394578794e-31</v>
       </c>
       <c r="B15" t="n">
-        <v>100.8222223966858</v>
+        <v>11.65454929809405</v>
       </c>
       <c r="C15" t="n">
-        <v>50.26615240217648</v>
+        <v>2.951684577305415</v>
       </c>
       <c r="D15" t="n">
-        <v>10.50214298883856</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8630218609018455</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -480,75 +480,75 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.725633230170963e-31</v>
+        <v>13.47774891631924</v>
       </c>
       <c r="B2" t="n">
-        <v>3.269820195722319</v>
+        <v>-72.00936976614922</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.609241807566864</v>
+        <v>-34.25216425596847</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2029582331677464</v>
+        <v>-2.811438983146238</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004280345960595156</v>
+        <v>0.09277585571694945</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.0004908700000088073</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>180</v>
       </c>
-      <c r="I2" t="n">
-        <v>180</v>
-      </c>
-      <c r="J2" t="n">
-        <v>90</v>
-      </c>
       <c r="K2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.479114197289397e-31</v>
+        <v>-7.772383609049233</v>
       </c>
       <c r="B3" t="n">
-        <v>-4.10834876046941</v>
+        <v>50.36154278639225</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7707132428197744</v>
+        <v>11.47090011521701</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0008560691557944053</v>
+        <v>2.122940732096838</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.241911979886173e-20</v>
+        <v>-0.1165421032237456</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0004908700000088066</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I3" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="J3" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L3" t="n">
         <v>90</v>
@@ -556,28 +556,28 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>6.972533808792097</v>
       </c>
       <c r="B4" t="n">
-        <v>6.894220277191542</v>
+        <v>107.2308603668059</v>
       </c>
       <c r="C4" t="n">
-        <v>2.015158273902357</v>
+        <v>54.42167729600679</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2029582331677464</v>
+        <v>9.180845729239461</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.007819188087690263</v>
+        <v>0.07414737338717628</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.002454350000002935</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>180</v>
+        <v>-180</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
         <v>-90</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L4" t="n">
         <v>90</v>
@@ -594,22 +594,22 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>11.22292532591712</v>
       </c>
       <c r="B5" t="n">
-        <v>-6.894220277191542</v>
+        <v>-80.64165378982474</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.015158273902357</v>
+        <v>-40.5206617459604</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2029582331677464</v>
+        <v>-6.716149939454543</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.05421614203604733</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.0004908699999853221</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -624,45 +624,45 @@
         <v>-90</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L5" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.465190328815662e-32</v>
+        <v>4.912938711212601</v>
       </c>
       <c r="B6" t="n">
-        <v>-2.863903729386826</v>
+        <v>42.58138142394621</v>
       </c>
       <c r="C6" t="n">
-        <v>2.015158273902358</v>
+        <v>54.71371440060757</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2029582331677464</v>
+        <v>9.266341622255835</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.1026285514034496</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.002454350000002935</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J6" t="n">
         <v>-90</v>
       </c>
       <c r="K6" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="L6" t="n">
         <v>90</v>
@@ -670,75 +670,75 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.465190328815662e-32</v>
+        <v>1.038274895355398</v>
       </c>
       <c r="B7" t="n">
-        <v>2.863903729386825</v>
+        <v>-34.00100282035061</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.015158273902358</v>
+        <v>-44.34289242548079</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2029582331677464</v>
+        <v>-7.409164794611282</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.007819188087690263</v>
+        <v>-0.0312622979940821</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.0004908699999853231</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>90</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K7" t="n">
+        <v>90</v>
+      </c>
+      <c r="L7" t="n">
         <v>-180</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-180</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-90</v>
-      </c>
-      <c r="K7" t="n">
-        <v>180</v>
-      </c>
-      <c r="L7" t="n">
-        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>2.233718475185733</v>
       </c>
       <c r="B8" t="n">
-        <v>-6.488303810856049</v>
+        <v>9.715152813900735</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.609241807566865</v>
+        <v>10.44772444685643</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.13038316942368</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.1880371794709396</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.002454350000002935</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="L8" t="n">
         <v>90</v>
@@ -746,75 +746,75 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>-0.4536655114448799</v>
       </c>
       <c r="B9" t="n">
-        <v>-6.894220277191542</v>
+        <v>2.862344280065093</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.015158273902358</v>
+        <v>-2.879394166354958</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2029582331677464</v>
+        <v>-9.671045523163453</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.007819188087690263</v>
+        <v>0.1661661157091655</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.001472609999985322</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="K9" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="L9" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>2.098794470644656</v>
       </c>
       <c r="B10" t="n">
-        <v>-6.488303810856049</v>
+        <v>9.173383996798824</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.609241807566865</v>
+        <v>10.1339097718287</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.04452263647013</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.8641756390893633</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.001472609999979452</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>90</v>
@@ -822,60 +822,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>2.271418918734376</v>
       </c>
       <c r="B11" t="n">
-        <v>-6.488303810856049</v>
+        <v>9.956871465341285</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.609241807566865</v>
+        <v>10.51869565412466</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.03060693251959</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007819188087690263</v>
+        <v>-0.8573084985497497</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0.0004908700000205485</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>5.736607171775577</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-79.14258238567194</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-35.40452142225948</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2.017059303794476</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.01362087101736764</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.003436090000008806</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -890,30 +890,30 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>5.593003761241677</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-78.25866068004262</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-34.34950321264454</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3.243174017395036</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.01367252879253835</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.002454350000008806</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -928,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -968,22 +968,22 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.725633230170963e-31</v>
+        <v>13.47774891631924</v>
       </c>
       <c r="B15" t="n">
-        <v>6.894220277191542</v>
+        <v>107.2308603668059</v>
       </c>
       <c r="C15" t="n">
-        <v>2.015158273902358</v>
+        <v>54.71371440060757</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2029582331677464</v>
+        <v>10.13038316942368</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007819188087690263</v>
+        <v>0.8641756390893633</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.003436090000008806</v>
       </c>
     </row>
   </sheetData>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -480,22 +480,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13.47774891631924</v>
+        <v>10.20241688096769</v>
       </c>
       <c r="B2" t="n">
-        <v>-72.00936976614922</v>
+        <v>-51.08155090132491</v>
       </c>
       <c r="C2" t="n">
-        <v>-34.25216425596847</v>
+        <v>-22.7933814227316</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.811438983146238</v>
+        <v>-1.740564174316093</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09277585571694945</v>
+        <v>0.05619287391438826</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004908700000088073</v>
+        <v>0.0004908700000088069</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -510,27 +510,27 @@
         <v>180</v>
       </c>
       <c r="K2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-7.772383609049233</v>
+        <v>-5.290733031250725</v>
       </c>
       <c r="B3" t="n">
-        <v>50.36154278639225</v>
+        <v>38.6883258584235</v>
       </c>
       <c r="C3" t="n">
-        <v>11.47090011521701</v>
+        <v>9.047703354877688</v>
       </c>
       <c r="D3" t="n">
-        <v>2.122940732096838</v>
+        <v>1.28285349628316</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1165421032237456</v>
+        <v>-0.0701672651549502</v>
       </c>
       <c r="F3" t="n">
         <v>0.0004908700000088066</v>
@@ -556,19 +556,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6.972533808792097</v>
+        <v>5.938985313002886</v>
       </c>
       <c r="B4" t="n">
-        <v>107.2308603668059</v>
+        <v>75.98181890618442</v>
       </c>
       <c r="C4" t="n">
-        <v>54.42167729600679</v>
+        <v>36.19331783428503</v>
       </c>
       <c r="D4" t="n">
-        <v>9.180845729239461</v>
+        <v>5.26335277486748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07414737338717628</v>
+        <v>0.04488511875415421</v>
       </c>
       <c r="F4" t="n">
         <v>0.002454350000002935</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-180</v>
+        <v>180</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -594,19 +594,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11.22292532591712</v>
+        <v>8.712861580632017</v>
       </c>
       <c r="B5" t="n">
-        <v>-80.64165378982474</v>
+        <v>-56.06433124095879</v>
       </c>
       <c r="C5" t="n">
-        <v>-40.5206617459604</v>
+        <v>-26.27610193289824</v>
       </c>
       <c r="D5" t="n">
-        <v>-6.716149939454543</v>
+        <v>-3.723224855015485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05421614203604733</v>
+        <v>0.03384697848175559</v>
       </c>
       <c r="F5" t="n">
         <v>-0.0004908699999853221</v>
@@ -632,19 +632,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4.912938711212601</v>
+        <v>3.802259157163413</v>
       </c>
       <c r="B6" t="n">
-        <v>42.58138142394621</v>
+        <v>26.63651949907414</v>
       </c>
       <c r="C6" t="n">
-        <v>54.71371440060757</v>
+        <v>36.51337799168403</v>
       </c>
       <c r="D6" t="n">
-        <v>9.266341622255835</v>
+        <v>5.316335649682959</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1026285514034496</v>
+        <v>0.06252644241314888</v>
       </c>
       <c r="F6" t="n">
         <v>0.002454350000002935</v>
@@ -670,19 +670,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.038274895355398</v>
+        <v>0.5612445370203584</v>
       </c>
       <c r="B7" t="n">
-        <v>-34.00100282035061</v>
+        <v>-22.81515460382354</v>
       </c>
       <c r="C7" t="n">
-        <v>-44.34289242548079</v>
+        <v>-29.06319697823687</v>
       </c>
       <c r="D7" t="n">
-        <v>-7.409164794611282</v>
+        <v>-4.164466565455585</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0312622979940821</v>
+        <v>-0.01911626172420416</v>
       </c>
       <c r="F7" t="n">
         <v>-0.0004908699999853231</v>
@@ -708,19 +708,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.233718475185733</v>
+        <v>1.23089958172399</v>
       </c>
       <c r="B8" t="n">
-        <v>9.715152813900735</v>
+        <v>4.811234318230071</v>
       </c>
       <c r="C8" t="n">
-        <v>10.44772444685643</v>
+        <v>5.898938693097441</v>
       </c>
       <c r="D8" t="n">
-        <v>10.13038316942368</v>
+        <v>5.863582378979679</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1880371794709396</v>
+        <v>0.1154111441611366</v>
       </c>
       <c r="F8" t="n">
         <v>0.002454350000002935</v>
@@ -746,19 +746,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.4536655114448799</v>
+        <v>-0.5757737499049899</v>
       </c>
       <c r="B9" t="n">
-        <v>2.862344280065093</v>
+        <v>1.607468904054138</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.879394166354958</v>
+        <v>-1.434825570012902</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.671045523163453</v>
+        <v>-5.600180733065074</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1661661157091655</v>
+        <v>0.1023938979680933</v>
       </c>
       <c r="F9" t="n">
         <v>0.001472609999985322</v>
@@ -784,19 +784,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.098794470644656</v>
+        <v>1.149952597581742</v>
       </c>
       <c r="B10" t="n">
-        <v>9.173383996798824</v>
+        <v>4.475683099361846</v>
       </c>
       <c r="C10" t="n">
-        <v>10.1339097718287</v>
+        <v>5.704635871188161</v>
       </c>
       <c r="D10" t="n">
-        <v>10.04452263647013</v>
+        <v>5.810527954029345</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8641756390893633</v>
+        <v>0.4871734209400908</v>
       </c>
       <c r="F10" t="n">
         <v>0.001472609999979452</v>
@@ -822,19 +822,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.271418918734376</v>
+        <v>1.257153919485134</v>
       </c>
       <c r="B11" t="n">
-        <v>9.956871465341285</v>
+        <v>4.961392830305935</v>
       </c>
       <c r="C11" t="n">
-        <v>10.51869565412466</v>
+        <v>5.943406340135321</v>
       </c>
       <c r="D11" t="n">
-        <v>10.03060693251959</v>
+        <v>5.802359160979575</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8573084985497497</v>
+        <v>-0.4808182805149171</v>
       </c>
       <c r="F11" t="n">
         <v>-0.0004908700000205485</v>
@@ -852,27 +852,27 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>180</v>
+      </c>
+      <c r="L11" t="n">
         <v>-180</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.736607171775577</v>
+        <v>5.246506406687828</v>
       </c>
       <c r="B12" t="n">
-        <v>-79.14258238567194</v>
+        <v>-55.64134205681706</v>
       </c>
       <c r="C12" t="n">
-        <v>-35.40452142225948</v>
+        <v>-23.54071019335533</v>
       </c>
       <c r="D12" t="n">
-        <v>2.017059303794476</v>
+        <v>1.324569439928595</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01362087101736764</v>
+        <v>-0.0121404359254656</v>
       </c>
       <c r="F12" t="n">
         <v>0.003436090000008806</v>
@@ -898,19 +898,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5.593003761241677</v>
+        <v>5.158135872179554</v>
       </c>
       <c r="B13" t="n">
-        <v>-78.25866068004262</v>
+        <v>-55.19019540189476</v>
       </c>
       <c r="C13" t="n">
-        <v>-34.34950321264454</v>
+        <v>-22.98347998110509</v>
       </c>
       <c r="D13" t="n">
-        <v>3.243174017395036</v>
+        <v>1.987883209506788</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01367252879253835</v>
+        <v>0.0121920937006363</v>
       </c>
       <c r="F13" t="n">
         <v>-0.002454350000008806</v>
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13.47774891631924</v>
+        <v>10.20241688096769</v>
       </c>
       <c r="B15" t="n">
-        <v>107.2308603668059</v>
+        <v>75.98181890618442</v>
       </c>
       <c r="C15" t="n">
-        <v>54.71371440060757</v>
+        <v>36.51337799168403</v>
       </c>
       <c r="D15" t="n">
-        <v>10.13038316942368</v>
+        <v>5.863582378979679</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8641756390893633</v>
+        <v>0.4871734209400908</v>
       </c>
       <c r="F15" t="n">
         <v>0.003436090000008806</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -505,22 +505,22 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1.455461741433114</v>
+        <v>2.911474869266255</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-5.898434954418077</v>
+        <v>-23.99358818062564</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-1.792054930505438</v>
+        <v>-11.0127321779106</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.1745857459773711</v>
+        <v>-0.9462280589048256</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.003675867724341084</v>
+        <v>0.03666776001633141</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.009817399999985333</v>
+        <v>0.0004908700000088073</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -532,71 +532,71 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-0.9230951311166126</v>
+        <v>-1.681896275843229</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.425053628939835</v>
+        <v>16.14488147350946</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.590031164943271</v>
+        <v>2.89623091389855</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.131224669708086</v>
+        <v>0.841599514076277</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.01064212512591806</v>
+        <v>-0.04072142657996321</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.004908699999985333</v>
+        <v>0.0004908700000088066</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>0.3167630187071376</v>
+        <v>0.8952603042921742</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8.683536834757598</v>
+        <v>33.55314466865428</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2.475309856539639</v>
+        <v>17.66682895874298</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.1089717314223301</v>
+        <v>4.979017594762969</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.02427258644208866</v>
+        <v>0.02531637237943481</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.02945220000002642</v>
+        <v>0.002454350000002935</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>-90</v>
@@ -619,22 +619,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1.095733779132227</v>
+        <v>2.519978262692992</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-6.460633841089736</v>
+        <v>-28.52551696704832</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-1.892471463326345</v>
+        <v>-14.87796770679228</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.1867800750524727</v>
+        <v>-4.144770330245511</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.005075444398022168</v>
+        <v>0.01421278339206292</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.001472609999735809</v>
+        <v>-0.0004908699999853231</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -646,33 +646,33 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>-0.3036964103526884</v>
+        <v>0.6027598007173629</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.1629652474239354</v>
+        <v>14.57710880712697</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2.737021714990513</v>
+        <v>17.73756768671248</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.335062004482657</v>
+        <v>5.002565539125406</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.01926897797286692</v>
+        <v>0.03315696067232133</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.02552523999999706</v>
+        <v>0.002454350000002935</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -695,22 +695,22 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>0.4025321740977112</v>
+        <v>0.7750829149053979</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-2.341214926799968</v>
+        <v>-14.47210881037885</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-2.100986163093049</v>
+        <v>-15.53223682110599</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1575954374275687</v>
+        <v>-4.340877757107775</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.03045989247400154</v>
+        <v>-0.009326434477261657</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.02356175999997358</v>
+        <v>-0.0004908699999853231</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -722,7 +722,7 @@
         <v>-90</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>90</v>
@@ -733,22 +733,22 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>0.03700043683627478</v>
+        <v>0.5735464385195248</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.461204162749288</v>
+        <v>2.93989580602531</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.424808385490066</v>
+        <v>4.394542081715426</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.4336263863900389</v>
+        <v>5.245786307701725</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.02015822119890796</v>
+        <v>0.05666127256031588</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.02552523999999706</v>
+        <v>0.002454350000002935</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>0.1996917530695035</v>
+        <v>0.178939844870325</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.6213285912011228</v>
+        <v>-3.617165075521839</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.4093663695862117</v>
+        <v>-3.998073843802572</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-0.3753651533504178</v>
+        <v>-4.982384661787121</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.02559865857350466</v>
+        <v>0.04353494517561621</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-0.01865305999994422</v>
+        <v>0.001472609999985322</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>180</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>-180</v>
@@ -809,22 +809,22 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>0.03214072833503762</v>
+        <v>0.5220343848330977</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.491328918462403</v>
+        <v>2.790656732185631</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.4531860938705782</v>
+        <v>4.308080073190833</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.4069957253421301</v>
+        <v>5.22210136449222</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.03664774306044759</v>
+        <v>0.4381042953945563</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-0.01963480000000293</v>
+        <v>0.001472609999979452</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -839,30 +839,30 @@
         <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>0.1941491119611811</v>
+        <v>0.5704312945398406</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.5894015191703375</v>
+        <v>3.002054954070348</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.3789036598458906</v>
+        <v>4.409727511965804</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-0.3463668059005607</v>
+        <v>5.213998020157445</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.02834954438849889</v>
+        <v>-0.4317491549693826</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.02454350000005578</v>
+        <v>-0.0004908700000205485</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -874,33 +874,33 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-90</v>
+        <v>-180</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1.119779107733567</v>
+        <v>0.8187480987494764</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-6.430440049308114</v>
+        <v>-25.96478666261651</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-1.869574014457161</v>
+        <v>-11.28950293329328</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.202381181009221</v>
+        <v>0.4714289123206778</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.02449597878853042</v>
+        <v>0.007537391640910136</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.02945220000002642</v>
+        <v>0.003436090000008806</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -923,22 +923,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1.071504183221239</v>
+        <v>0.7697332193739543</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-6.459866295782994</v>
+        <v>-25.33696497624429</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-1.89885891841097</v>
+        <v>-10.61453299921975</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.1732376195764808</v>
+        <v>1.193547094095521</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.03008900900451773</v>
+        <v>-0.007485733865739447</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-0.02356176000002642</v>
+        <v>-0.002454350000008806</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -999,22 +999,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1.455461741433114</v>
+        <v>2.911474869266255</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>8.683536834757598</v>
+        <v>33.55314466865428</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2.737021714990513</v>
+        <v>17.73756768671248</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.4336263863900389</v>
+        <v>5.245786307701725</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.03664774306044759</v>
+        <v>0.4381042953945563</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.02945220000002642</v>
+        <v>0.003436090000008806</v>
       </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -505,22 +505,22 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>2.911474869266255</v>
+        <v>6.761431925735247</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-23.99358818062564</v>
+        <v>-41.62308319710549</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-11.0127321779106</v>
+        <v>-15.87577914060024</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.9462280589048256</v>
+        <v>-1.354184356702171</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.03666776001633141</v>
+        <v>0.0483893732266649</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0004908700000088073</v>
+        <v>0.0004908700000088069</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -535,27 +535,27 @@
         <v>180</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-1.681896275843229</v>
+        <v>-3.236738517880381</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>16.14488147350946</v>
+        <v>32.56041743655345</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2.89623091389855</v>
+        <v>5.396378106177538</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.841599514076277</v>
+        <v>1.116163546884755</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.04072142657996321</v>
+        <v>-0.04858819435884724</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.0004908700000088066</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>0.8952603042921742</v>
+        <v>3.567222801850561</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>33.55314466865428</v>
+        <v>58.86926967563699</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>17.66682895874298</v>
+        <v>24.9473376535602</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4.979017594762969</v>
+        <v>5.131971243283288</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.02531637237943481</v>
+        <v>0.03705980182809959</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.002454350000002935</v>
@@ -619,22 +619,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2.519978262692992</v>
+        <v>5.711100102904539</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-28.52551696704832</v>
+        <v>-46.52357662888603</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-14.87796770679228</v>
+        <v>-19.44288605729878</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-4.144770330245511</v>
+        <v>-3.921251387089211</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.01421278339206292</v>
+        <v>0.02599111882203716</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.0004908699999853231</v>
+        <v>-0.0004908699999853221</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -652,24 +652,24 @@
         <v>90</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-180</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>0.6027598007173629</v>
+        <v>2.026733107327311</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>14.57710880712697</v>
+        <v>18.02621038034533</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>17.73756768671248</v>
+        <v>25.14269115737128</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5.002565539125406</v>
+        <v>5.179067132008158</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.03315696067232133</v>
+        <v>0.05274097841387262</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.002454350000002935</v>
@@ -695,19 +695,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>0.7750829149053979</v>
+        <v>0.2979884423806084</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-14.47210881037885</v>
+        <v>-17.55174729572954</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-15.53223682110599</v>
+        <v>-21.21568061191953</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-4.340877757107775</v>
+        <v>-4.313466240813745</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.009326434477261657</v>
+        <v>-0.02108731691659144</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>-0.0004908699999853231</v>
@@ -733,19 +733,19 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>0.5735464385195248</v>
+        <v>0.9451422441910399</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.93989580602531</v>
+        <v>2.984100699104122</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4.394542081715426</v>
+        <v>4.947327690306488</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5.245786307701725</v>
+        <v>5.543898284872639</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.05666127256031588</v>
+        <v>0.08799744624586445</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.002454350000002935</v>
@@ -771,19 +771,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>0.178939844870325</v>
+        <v>-0.2025666097140424</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-3.617165075521839</v>
+        <v>-1.415851570828583</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-3.998073843802572</v>
+        <v>-3.123734667567913</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-4.982384661787121</v>
+        <v>-5.280496638958034</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.04353494517561621</v>
+        <v>0.07492347783315981</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.001472609999985322</v>
@@ -809,19 +809,19 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>0.5220343848330977</v>
+        <v>0.8779315609281751</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.790656732185631</v>
+        <v>2.725032303696702</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4.308080073190833</v>
+        <v>4.813813425529243</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5.22210136449222</v>
+        <v>5.504549618068024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.4381042953945563</v>
+        <v>0.4616609662545459</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.001472609999979452</v>
@@ -847,19 +847,19 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>0.5704312945398406</v>
+        <v>0.9576908238064639</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.002054954070348</v>
+        <v>3.101021794264708</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4.409727511965804</v>
+        <v>4.970301349877756</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5.213998020157445</v>
+        <v>5.496411367751919</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.4317491549693826</v>
+        <v>-0.4553058258293721</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>-0.0004908700000205485</v>
@@ -877,27 +877,27 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>-180</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>0.8187480987494764</v>
+        <v>2.950781843217621</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-25.96478666261651</v>
+        <v>-45.28864832024242</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-11.28950293329328</v>
+        <v>-16.15248881052078</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.4714289123206778</v>
+        <v>0.9107475632895692</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.007537391640910136</v>
+        <v>-0.004262760027415929</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.003436090000008806</v>
@@ -923,19 +923,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>0.7697332193739543</v>
+        <v>2.878166660505447</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-25.33696497624429</v>
+        <v>-44.7629113585937</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-10.61453299921975</v>
+        <v>-15.53245535346945</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.193547094095521</v>
+        <v>1.601503391892866</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.007485733865739447</v>
+        <v>0.004314417802586619</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>-0.002454350000008806</v>
@@ -999,19 +999,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>2.911474869266255</v>
+        <v>6.761431925735247</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>33.55314466865428</v>
+        <v>58.86926967563699</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>17.73756768671248</v>
+        <v>25.14269115737128</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5.245786307701725</v>
+        <v>5.543898284872639</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.4381042953945563</v>
+        <v>0.4616609662545459</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.003436090000008806</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -505,75 +505,75 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6.761431925735247</v>
+        <v>1.725633230170963e-31</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-41.62308319710549</v>
+        <v>3.269820195722319</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-15.87577914060024</v>
+        <v>-1.609241807566864</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-1.354184356702171</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0483893732266649</v>
+        <v>0.0004280345960595156</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0004908700000088069</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>90</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-3.236738517880381</v>
+        <v>-1.479114197289397e-31</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>32.56041743655345</v>
+        <v>-4.10834876046941</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.396378106177538</v>
+        <v>0.7707132428197744</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.116163546884755</v>
+        <v>-0.0008560691557944053</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.04858819435884724</v>
+        <v>-5.241911979886173e-20</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0004908700000088066</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>90</v>
@@ -581,22 +581,22 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3.567222801850561</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>58.86926967563699</v>
+        <v>6.894220277191542</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>24.9473376535602</v>
+        <v>2.015158273902357</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5.131971243283288</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.03705980182809959</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.002454350000002935</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -611,7 +611,7 @@
         <v>-90</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>90</v>
@@ -619,22 +619,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.711100102904539</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-46.52357662888603</v>
+        <v>-6.894220277191542</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-19.44288605729878</v>
+        <v>-2.015158273902357</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-3.921251387089211</v>
+        <v>-0.2029582331677464</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.02599111882203716</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.0004908699999853221</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -649,45 +649,45 @@
         <v>-90</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2.026733107327311</v>
+        <v>2.465190328815662e-32</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>18.02621038034533</v>
+        <v>-2.863903729386826</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25.14269115737128</v>
+        <v>2.015158273902358</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5.179067132008158</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.05274097841387262</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.002454350000002935</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>-90</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>90</v>
@@ -695,75 +695,75 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>0.2979884423806084</v>
+        <v>2.465190328815662e-32</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-17.55174729572954</v>
+        <v>2.863903729386825</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-21.21568061191953</v>
+        <v>-2.015158273902358</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-4.313466240813745</v>
+        <v>-0.2029582331677464</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.02108731691659144</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.0004908699999853231</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-90</v>
+        <v>-180</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>-90</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>0.9451422441910399</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.984100699104122</v>
+        <v>-6.488303810856049</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4.947327690306488</v>
+        <v>-1.609241807566865</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5.543898284872639</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.08799744624586445</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.002454350000002935</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>90</v>
@@ -771,75 +771,75 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>-0.2025666097140424</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.415851570828583</v>
+        <v>-6.894220277191542</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-3.123734667567913</v>
+        <v>-2.015158273902358</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-5.280496638958034</v>
+        <v>-0.2029582331677464</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.07492347783315981</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.001472609999985322</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>-90</v>
-      </c>
       <c r="L9" s="2" t="n">
-        <v>-180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>0.8779315609281751</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.725032303696702</v>
+        <v>-6.488303810856049</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4.813813425529243</v>
+        <v>-1.609241807566865</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5.504549618068024</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.4616609662545459</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.001472609999979452</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>90</v>
@@ -847,60 +847,60 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>0.9576908238064639</v>
+        <v>-9.860761315262648e-32</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.101021794264708</v>
+        <v>-6.488303810856049</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4.970301349877756</v>
+        <v>-1.609241807566865</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5.496411367751919</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.4553058258293721</v>
+        <v>-0.007819188087690263</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.0004908700000205485</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2.950781843217621</v>
+        <v>0</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-45.28864832024242</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-16.15248881052078</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.9107475632895692</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.004262760027415929</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.003436090000008806</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -915,30 +915,30 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2.878166660505447</v>
+        <v>0</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-44.7629113585937</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-15.53245535346945</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.601503391892866</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.004314417802586619</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-0.002454350000008806</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row customHeight="1" ht="40" r="14">
@@ -999,22 +999,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.761431925735247</v>
+        <v>1.725633230170963e-31</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>58.86926967563699</v>
+        <v>6.894220277191542</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>25.14269115737128</v>
+        <v>2.015158273902358</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5.543898284872639</v>
+        <v>0.2029582331677464</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.4616609662545459</v>
+        <v>0.007819188087690263</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.003436090000008806</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -505,19 +505,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1.725633230170963e-31</v>
+        <v>110.7966799321688</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.269820195722319</v>
+        <v>-41.66414958356769</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-1.609241807566864</v>
+        <v>-62.15189586582674</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.2029582331677464</v>
+        <v>-3.191627486732149</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0004280345960595156</v>
+        <v>18.46246099450316</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -526,16 +526,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>90</v>
@@ -543,19 +543,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-1.479114197289397e-31</v>
+        <v>-94.38054279138252</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-4.10834876046941</v>
+        <v>83.52746004302472</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.7707132428197744</v>
+        <v>87.49448171138745</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.0008560691557944053</v>
+        <v>12.17445428534336</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-5.241911979886173e-20</v>
+        <v>-14.59811198587169</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -564,16 +564,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>-90</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>90</v>
-      </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>90</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>0</v>
+        <v>49.77579149448863</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6.894220277191542</v>
+        <v>201.7440721005563</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2.015158273902357</v>
+        <v>77.2488111993589</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2029582331677464</v>
+        <v>-16.1215208360888</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.007819188087690263</v>
+        <v>-18.71546663806172</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -608,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-90</v>
+        <v>-180</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>90</v>
@@ -619,19 +619,19 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>-14.28288014859879</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-6.894220277191542</v>
+        <v>-153.7731379200286</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-2.015158273902357</v>
+        <v>-54.14235998573314</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.2029582331677464</v>
+        <v>18.56706619367415</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.007819188087690263</v>
+        <v>21.67615433845044</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>90</v>
@@ -657,19 +657,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2.465190328815662e-32</v>
+        <v>42.86009823796832</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-2.863903729386826</v>
+        <v>42.82863301204491</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2.015158273902358</v>
+        <v>91.05557242059682</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.2029582331677464</v>
+        <v>-10.15537154100048</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.007819188087690263</v>
+        <v>-11.74958409994647</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>180</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>-90</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>180</v>
@@ -695,19 +695,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2.465190328815662e-32</v>
+        <v>-34.33860248089776</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.863903729386825</v>
+        <v>-7.566456761511258</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-2.015158273902358</v>
+        <v>-73.4859475337616</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.2029582331677464</v>
+        <v>14.23051558277497</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.007819188087690263</v>
+        <v>16.64800433636307</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -716,13 +716,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>-180</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-180</v>
+        <v>-90</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>180</v>
@@ -733,19 +733,19 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>-51.28836170600538</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-6.488303810856049</v>
+        <v>106.8886430392282</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-1.609241807566865</v>
+        <v>57.86802543623783</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.2029582331677464</v>
+        <v>35.95772801292233</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.007819188087690263</v>
+        <v>-2.369602705869433</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -754,16 +754,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>90</v>
@@ -771,19 +771,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>1.198394629705947</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-6.894220277191542</v>
+        <v>-27.34835394991585</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.015158273902358</v>
+        <v>43.47579739043305</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-0.2029582331677464</v>
+        <v>-29.0517940450606</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.007819188087690263</v>
+        <v>-4.269531767951848</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -795,13 +795,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J9" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-90</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>180</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>90</v>
@@ -809,19 +809,19 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>14.39283721888997</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-6.488303810856049</v>
+        <v>-19.0752069367128</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-1.609241807566865</v>
+        <v>1.705786868302846</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.2029582331677464</v>
+        <v>22.51410084430155</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.007819188087690263</v>
+        <v>28.33843135912063</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -830,36 +830,36 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>180</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>-9.860761315262648e-32</v>
+        <v>-2.226200257019574</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-6.488303810856049</v>
+        <v>91.63597827054394</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-1.609241807566865</v>
+        <v>37.9675228497828</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.2029582331677464</v>
+        <v>-11.7135353135178</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.007819188087690263</v>
+        <v>-26.74751534303447</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -868,19 +868,19 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="12">
@@ -999,19 +999,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1.725633230170963e-31</v>
+        <v>110.7966799321688</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>6.894220277191542</v>
+        <v>201.7440721005563</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2.015158273902358</v>
+        <v>91.05557242059682</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.2029582331677464</v>
+        <v>35.95772801292233</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.007819188087690263</v>
+        <v>28.33843135912063</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -505,22 +505,22 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>110.7966799321688</v>
+        <v>82.2113004966656</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-41.66414958356769</v>
+        <v>-5.592517658345071</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-62.15189586582674</v>
+        <v>-34.80436492885886</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-3.191627486732149</v>
+        <v>5.617367179445602</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18.46246099450316</v>
+        <v>-0.8622268599927165</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.01461197360960041</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -532,33 +532,33 @@
         <v>-90</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>-90</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-94.38054279138252</v>
+        <v>-73.18262285766893</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>83.52746004302472</v>
+        <v>16.42679212082324</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>87.49448171138745</v>
+        <v>53.88995629352218</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12.17445428534336</v>
+        <v>6.249513966868148</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-14.59811198587169</v>
+        <v>-0.9000496813098784</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.001546240546840751</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -573,7 +573,7 @@
         <v>-90</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>90</v>
@@ -581,98 +581,98 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>49.77579149448863</v>
+        <v>-43.13473955424504</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>201.7440721005563</v>
+        <v>142.0559166323473</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>77.2488111993589</v>
+        <v>29.83127157747576</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-16.1215208360888</v>
+        <v>4.179484679111317</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-18.71546663806172</v>
+        <v>0.3765394728115334</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>0.001314304317514083</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="J4" s="2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>-180</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>-180</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>-14.28288014859879</v>
+        <v>54.02725600000286</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-153.7731379200286</v>
+        <v>-88.88192012164426</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-54.14235998573314</v>
+        <v>-4.505054443643257</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>18.56706619367415</v>
+        <v>0.5412985202145802</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>21.67615433845044</v>
+        <v>0.4096045922130492</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>-0.01151949251605391</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>42.86009823796832</v>
+        <v>28.44758721542584</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>42.82863301204491</v>
+        <v>-26.35300974234124</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>91.05557242059682</v>
+        <v>66.09913621991822</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-10.15537154100048</v>
+        <v>7.941290759183584</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-11.74958409994647</v>
+        <v>0.5197440552510905</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>0.01770445470336143</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -684,10 +684,10 @@
         <v>90</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>90</v>
@@ -695,22 +695,22 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>-34.33860248089776</v>
+        <v>-27.63904069235715</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-7.566456761511258</v>
+        <v>36.25169149877637</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-73.4859475337616</v>
+        <v>-45.17193196963346</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14.23051558277497</v>
+        <v>12.96397855963378</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16.64800433636307</v>
+        <v>1.079164572651218</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>0.00618496218707728</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>90</v>
@@ -733,28 +733,28 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>-51.28836170600538</v>
+        <v>-7.861230335543903</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>106.8886430392282</v>
+        <v>73.32558457604661</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>57.86802543623783</v>
+        <v>37.67232410116509</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35.95772801292233</v>
+        <v>17.34534641235652</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.369602705869433</v>
+        <v>-0.06126754204907255</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>0.001546240546840751</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>-180</v>
+        <v>180</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>90</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1.198394629705947</v>
+        <v>77.40839609967408</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-27.34835394991585</v>
+        <v>-12.1975438807355</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>43.47579739043305</v>
+        <v>-13.37096341855925</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-29.0517940450606</v>
+        <v>-16.41680418391818</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-4.269531767951848</v>
+        <v>0.3177965070105712</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>0.001546240546840753</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -795,36 +795,36 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>14.39283721888997</v>
+        <v>3.207256188159779</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-19.0752069367128</v>
+        <v>1.411029972982779</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.705786868302846</v>
+        <v>5.687996310871313</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>22.51410084430155</v>
+        <v>16.71076210082571</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>28.33843135912063</v>
+        <v>1.421686886115156</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>0.001314304317146057</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -839,68 +839,68 @@
         <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>-2.226200257019574</v>
+        <v>22.55269956278405</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>91.63597827054394</v>
+        <v>-60.99586774708909</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>37.9675228497828</v>
+        <v>-21.11623517719973</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-11.7135353135178</v>
+        <v>16.89097616515445</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-26.74751534303447</v>
+        <v>-1.406422058086497</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>-0.003092481093800791</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>-90</v>
-      </c>
       <c r="L11" s="2" t="n">
-        <v>-90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>0</v>
+        <v>21.35824886311809</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0</v>
+        <v>-63.15271472487846</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>-22.29284742159912</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>16.69459865414505</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>0.1060908189592196</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>0.0307701877663726</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -915,30 +915,30 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>0</v>
+        <v>20.93450078481303</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>-63.5001517568219</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>-22.26721898583223</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>17.09329255762226</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>-0.1055782446540517</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>-0.02767770667274658</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row customHeight="1" ht="40" r="14">
@@ -999,22 +999,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>110.7966799321688</v>
+        <v>82.2113004966656</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>201.7440721005563</v>
+        <v>142.0559166323473</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>91.05557242059682</v>
+        <v>66.09913621991822</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35.95772801292233</v>
+        <v>17.34534641235652</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>28.33843135912063</v>
+        <v>1.421686886115156</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>0.0307701877663726</v>
       </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="20"/>
@@ -439,6 +439,8 @@
     <col customWidth="1" max="10" min="10" width="20"/>
     <col customWidth="1" max="11" min="11" width="20"/>
     <col customWidth="1" max="12" min="12" width="20"/>
+    <col customWidth="1" max="13" min="13" width="20"/>
+    <col customWidth="1" max="14" min="14" width="20"/>
   </cols>
   <sheetData>
     <row customHeight="1" ht="40" r="1">
@@ -474,53 +476,63 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>torque 7</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>angle 1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>angle 2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>angle 3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>angle 4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>angle 5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>angle 6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>angle 7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>82.2113004966656</v>
+        <v>13.53553917795789</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-5.592517658345071</v>
+        <v>25.78301066937767</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-34.80436492885886</v>
+        <v>-0.235622361829756</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5.617367179445602</v>
+        <v>-14.12942210942824</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.8622268599927165</v>
+        <v>-0.07475867073508852</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.01461197360960041</v>
+        <v>-5.703381322970143</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -529,83 +541,95 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-73.18262285766893</v>
+        <v>-8.380422796864671</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>16.42679212082324</v>
+        <v>-15.3012984782143</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>53.88995629352218</v>
+        <v>19.67080574244082</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6.249513966868148</v>
+        <v>-2.585999829416555</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.9000496813098784</v>
+        <v>0.08756984205622459</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.001546240546840751</v>
+        <v>7.756089995054865</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>-43.13473955424504</v>
+        <v>6.028287293409611</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>142.0559166323473</v>
+        <v>38.65065835253045</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>29.83127157747576</v>
+        <v>0.1996847654248843</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4.179484679111317</v>
+        <v>2.78044114928671</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3765394728115334</v>
+        <v>0.01712616547827133</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.001314304317514083</v>
+        <v>1.62685563127793</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>-90</v>
@@ -614,179 +638,209 @@
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-180</v>
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>54.02725600000286</v>
+        <v>5.895815703837757</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-88.88192012164426</v>
+        <v>-32.07925734277465</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-4.505054443643257</v>
+        <v>0.179659524382295</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5412985202145802</v>
+        <v>2.72561072237523</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4096045922130492</v>
+        <v>0.01432682069678612</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.01151949251605391</v>
+        <v>1.621265655342303</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>-90</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>90</v>
-      </c>
       <c r="J5" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-180</v>
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>28.44758721542584</v>
+        <v>-5.478591741607429</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-26.35300974234124</v>
+        <v>-16.93807527901166</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>66.09913621991822</v>
+        <v>22.41281570056159</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7.941290759183584</v>
+        <v>0.9469720293775645</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5197440552510905</v>
+        <v>0.01194859024070796</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.01770445470336143</v>
+        <v>0.6696237353034267</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>-27.63904069235715</v>
+        <v>10.7845860334369</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>36.25169149877637</v>
+        <v>13.66461836083642</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-45.17193196963346</v>
+        <v>-17.86751574178797</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12.96397855963378</v>
+        <v>3.610821960265803</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.079164572651218</v>
+        <v>0.01274790180115595</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.00618496218707728</v>
+        <v>2.054182770239327</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>-90</v>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>-7.861230335543903</v>
+        <v>2.846049532633103</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.32558457604661</v>
+        <v>-1.814593287030277</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>37.67232410116509</v>
+        <v>-2.846231752052053</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17.34534641235652</v>
+        <v>19.99253704893429</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.06126754204907255</v>
+        <v>0.09780063113598426</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.001546240546840751</v>
+        <v>8.516005218106921</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>77.40839609967408</v>
+        <v>6.332727872556736</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-12.1975438807355</v>
+        <v>-3.886375082522389</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-13.37096341855925</v>
+        <v>6.332924386673054</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-16.41680418391818</v>
+        <v>-18.64405374848144</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.3177965070105712</v>
+        <v>0.01983798218049579</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.001546240546840753</v>
+        <v>2.709222075769491</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -795,42 +849,48 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>90</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-180</v>
+        <v>90</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3.207256188159779</v>
+        <v>3.207433995534041</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.411029972982779</v>
+        <v>10.30512895131973</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5.687996310871313</v>
+        <v>-3.207616214952989</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>16.71076210082571</v>
+        <v>11.76274309876443</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.421686886115156</v>
+        <v>9.315549257660999</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.001314304317146057</v>
+        <v>-2.570620351302291</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
@@ -839,30 +899,36 @@
         <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L10" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="N10" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>22.55269956278405</v>
+        <v>12.79758804937431</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-60.99586774708909</v>
+        <v>25.96635204839817</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-21.11623517719973</v>
+        <v>-7.859878118380379</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>16.89097616515445</v>
+        <v>5.663032408108168</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1.406422058086497</v>
+        <v>-8.042436718326993</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.003092481093800791</v>
+        <v>-0.4173946982786467</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -871,36 +937,42 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-180</v>
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>21.35824886311809</v>
+        <v>0.415022018630777</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-63.15271472487846</v>
+        <v>0.2222489785473763</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-22.29284742159912</v>
+        <v>-0.4152042380497269</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16.69459865414505</v>
+        <v>-1.747805414266071</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.1060908189592196</v>
+        <v>-0.4065546797995624</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.0307701877663726</v>
+        <v>10.1489711387684</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -915,30 +987,36 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>-90</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="M12" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="N12" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>20.93450078481303</v>
+        <v>-2.651169556098034</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-63.5001517568219</v>
+        <v>6.689725765723887</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-22.26721898583223</v>
+        <v>2.650987336679085</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>17.09329255762226</v>
+        <v>1.532993152789851</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.1055782446540517</v>
+        <v>2.65963689492925</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-0.02767770667274658</v>
+        <v>-9.656375662774595</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -953,75 +1031,179 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>90</v>
       </c>
+      <c r="M13" s="2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row customHeight="1" ht="40" r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Torque 1 max</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Torque 2 max</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>Torque 3 max</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Torque 4 max</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>Torque 5 max</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Torque 6 max</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="n"/>
-      <c r="H14" s="1" t="n"/>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="n"/>
-      <c r="K14" s="1" t="n"/>
-      <c r="L14" s="1" t="n"/>
+      <c r="A14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>82.2113004966656</v>
+        <v>0</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>142.0559166323473</v>
+        <v>0</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>66.09913621991822</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>17.34534641235652</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.421686886115156</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.0307701877663726</v>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Torque 1 max</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Torque 2 max</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Torque 3 max</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Torque 4 max</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Torque 5 max</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Torque 6 max</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Torque 7 max</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>13.53553917795789</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>38.65065835253045</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>22.41281570056159</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>19.99253704893429</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>9.315549257660999</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>10.1489711387684</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -517,22 +517,22 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>13.53553917795789</v>
+        <v>3.944304526105059e-31</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>25.78301066937767</v>
+        <v>-8.41364346382081</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.235622361829756</v>
+        <v>0.1635899709951098</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-14.12942210942824</v>
+        <v>2.515714543312775</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.07475867073508852</v>
+        <v>0.0007568300337062456</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-5.703381322970143</v>
+        <v>-3.79405811189483e-17</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -541,19 +541,19 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>180</v>
+        <v>-180</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>90</v>
@@ -561,22 +561,22 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-8.380422796864671</v>
+        <v>-5.916456789157589e-31</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-15.3012984782143</v>
+        <v>8.41364346382081</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>19.67080574244082</v>
+        <v>-0.1635899709951098</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-2.585999829416555</v>
+        <v>-2.515714543312775</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.08756984205622459</v>
+        <v>-0.0007568300337062568</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>7.756089995054865</v>
+        <v>-1.897029197763442e-17</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -585,19 +585,19 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>-90</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>90</v>
-      </c>
       <c r="M3" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>90</v>
@@ -605,22 +605,22 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6.028287293409611</v>
+        <v>-1.97215226305253e-31</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>38.65065835253045</v>
+        <v>8.72345184270756</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1996847654248843</v>
+        <v>0.2356216378120972</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2.78044114928671</v>
+        <v>2.825522922199525</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01712616547827133</v>
+        <v>0.07278849685069361</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.62685563127793</v>
+        <v>0.1549041894433748</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>90</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -649,22 +649,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.895815703837757</v>
+        <v>0</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-32.07925734277465</v>
+        <v>-8.72345184270756</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.179659524382295</v>
+        <v>-0.2356216378120972</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.72561072237523</v>
+        <v>-2.825522922199525</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.01432682069678612</v>
+        <v>-0.07278849685069361</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.621265655342303</v>
+        <v>-0.1549041894433748</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>-90</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -693,22 +693,22 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>-5.478591741607429</v>
+        <v>0</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-16.93807527901166</v>
+        <v>6.357852002062653</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>22.41281570056159</v>
+        <v>3.442918480467286</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.9469720293775645</v>
+        <v>3.460267602589124e-16</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.01194859024070796</v>
+        <v>0.0007567837130766367</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6696237353034267</v>
+        <v>1.897029197763442e-17</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>-90</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>90</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>90</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>10.7845860334369</v>
+        <v>4.930380657631324e-32</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>13.66461836083642</v>
+        <v>6.357852002062653</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-17.86751574178797</v>
+        <v>-3.442918480467286</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3.610821960265803</v>
+        <v>5.632433296798498e-17</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.01274790180115595</v>
+        <v>-0.0007567837130766278</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.054182770239327</v>
+        <v>2.836320541018949e-24</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>90</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2.846049532633103</v>
+        <v>2.465190328815662e-32</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.814593287030277</v>
+        <v>3.439704723237628</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-2.846231752052053</v>
+        <v>4.21635909682953e-16</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19.99253704893429</v>
+        <v>2.825522922199525</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.09780063113598426</v>
+        <v>0.07278849685069361</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>8.516005218106921</v>
+        <v>0.1549041894433748</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>90</v>
@@ -825,22 +825,22 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.332727872556736</v>
+        <v>9.860761315262648e-32</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-3.886375082522389</v>
+        <v>-2.211341121161422</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6.332924386673054</v>
+        <v>-2.704176108348719e-16</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-18.64405374848144</v>
+        <v>-2.825522922199525</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.01983798218049579</v>
+        <v>-0.07278849685069361</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.709222075769491</v>
+        <v>-0.1549041894433748</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -849,16 +849,16 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -869,22 +869,22 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3.207433995534041</v>
+        <v>1.725633230170963e-31</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.30512895131973</v>
+        <v>-3.291228071413882</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-3.207616214952989</v>
+        <v>-4.026656205416392e-16</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11.76274309876443</v>
+        <v>2.670618755916465</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9.315549257660999</v>
+        <v>0.1556609963167663</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2.570620351302291</v>
+        <v>1.89702976502755e-17</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -896,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>90</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>90</v>
@@ -913,22 +913,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>12.79758804937431</v>
+        <v>1.479114197289397e-31</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>25.96635204839817</v>
+        <v>6.514269782092496</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-7.859878118380379</v>
+        <v>3.288014314184225</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5.663032408108168</v>
+        <v>3.270564711175985e-16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-8.042436718326993</v>
+        <v>-0.1556609963167663</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.4173946982786467</v>
+        <v>-1.89702976502755e-17</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>-90</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>90</v>
@@ -957,22 +957,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>0.415022018630777</v>
+        <v>3.081487911019577e-33</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.2222489785473763</v>
+        <v>0.3091629320871749</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.4152042380497269</v>
+        <v>3.82551112700106e-17</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-1.747805414266071</v>
+        <v>-0.3050188689509281</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.4065546797995624</v>
+        <v>1.906297408914157e-17</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>10.1489711387684</v>
+        <v>0.1549041894433748</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>90</v>
@@ -1001,22 +1001,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>-2.651169556098034</v>
+        <v>-7.113903732080352e-33</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>6.689725765723887</v>
+        <v>-0.0006454467995747181</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2.650987336679085</v>
+        <v>3.145273147417692e-19</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.532993152789851</v>
+        <v>-0.6148272478376777</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.65963689492925</v>
+        <v>-1.887760986612726e-17</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-9.656375662774595</v>
+        <v>-0.1549041894433748</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-90</v>
@@ -1177,22 +1177,22 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>13.53553917795789</v>
+        <v>3.944304526105059e-31</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>38.65065835253045</v>
+        <v>8.72345184270756</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>22.41281570056159</v>
+        <v>3.442918480467286</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>19.99253704893429</v>
+        <v>2.825522922199525</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9.315549257660999</v>
+        <v>0.1556609963167663</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>10.1489711387684</v>
+        <v>0.1549041894433748</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_limit_torque_calc.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="20"/>
@@ -439,8 +439,6 @@
     <col customWidth="1" max="10" min="10" width="20"/>
     <col customWidth="1" max="11" min="11" width="20"/>
     <col customWidth="1" max="12" min="12" width="20"/>
-    <col customWidth="1" max="13" min="13" width="20"/>
-    <col customWidth="1" max="14" min="14" width="20"/>
   </cols>
   <sheetData>
     <row customHeight="1" ht="40" r="1">
@@ -476,63 +474,53 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>torque 7</t>
+          <t>angle 1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>angle 1</t>
+          <t>angle 2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>angle 2</t>
+          <t>angle 3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>angle 3</t>
+          <t>angle 4</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>angle 4</t>
+          <t>angle 5</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>angle 5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>angle 6</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>angle 7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3.944304526105059e-31</v>
+        <v>22.60661927447309</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-8.41364346382081</v>
+        <v>-22.59356694474243</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.1635899709951098</v>
+        <v>-14.06881746673712</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2.515714543312775</v>
+        <v>-6.051374667215467</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0007568300337062456</v>
+        <v>0.1655815129150472</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3.79405811189483e-17</v>
+        <v>0.001156584958283194</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -541,130 +529,112 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>-90</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>-180</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" s="2" t="n">
-        <v>-90</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>-180</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>-5.916456789157589e-31</v>
+        <v>-18.45100483697522</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8.41364346382081</v>
+        <v>30.32353446810498</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.1635899709951098</v>
+        <v>21.63598421662745</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-2.515714543312775</v>
+        <v>1.701200208414609</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.0007568300337062568</v>
+        <v>0.2836898492433492</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1.897029197763442e-17</v>
+        <v>-0.008175415684367393</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>90</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>180</v>
+        <v>-180</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>-90</v>
       </c>
-      <c r="M3" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>90</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>-1.97215226305253e-31</v>
+        <v>12.96406004405746</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8.72345184270756</v>
+        <v>57.32907156079247</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.2356216378120972</v>
+        <v>28.00104595853756</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2.825522922199525</v>
+        <v>-5.470927493063819</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.07278849685069361</v>
+        <v>-0.4562877668026663</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1549041894433748</v>
+        <v>0.004626339833147555</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>0</v>
+        <v>3.34028712355232</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-8.72345184270756</v>
+        <v>-39.42535058705666</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.2356216378120972</v>
+        <v>-18.74577924073374</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-2.825522922199525</v>
+        <v>6.288414174432563</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.07278849685069361</v>
+        <v>0.5229734554954202</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1549041894433748</v>
+        <v>0.004626339832951993</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -673,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -682,39 +652,33 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>0</v>
+        <v>5.183317671921121</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.357852002062653</v>
+        <v>14.17102947076536</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3.442918480467286</v>
+        <v>34.88092866295083</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3.460267602589124e-16</v>
+        <v>6.002614967706206</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0007567837130766367</v>
+        <v>0.182295454986041</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.897029197763442e-17</v>
+        <v>0.01048858560098513</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>90</v>
@@ -723,86 +687,74 @@
         <v>-90</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.930380657631324e-32</v>
+        <v>-4.104398608859751</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.357852002062653</v>
+        <v>-8.20753999592924</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-3.442918480467286</v>
+        <v>-23.58822497645226</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5.632433296798498e-17</v>
+        <v>5.258950143876911</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.0007567837130766278</v>
+        <v>0.4373921972986484</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.836320541018949e-24</v>
+        <v>0.004626339832951993</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2.465190328815662e-32</v>
+        <v>3.107484036648333</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.439704723237628</v>
+        <v>1.267263831394952</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4.21635909682953e-16</v>
+        <v>4.146154727500027</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2.825522922199525</v>
+        <v>9.330657670349888</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.07278849685069361</v>
+        <v>0.4543963148261407</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1549041894433748</v>
+        <v>0.01048858560098513</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
@@ -811,168 +763,144 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>9.860761315262648e-32</v>
+        <v>-2.647647570629449</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-2.211341121161422</v>
+        <v>14.25217672214665</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.704176108348719e-16</v>
+        <v>4.205002015290807</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-2.825522922199525</v>
+        <v>-8.706986886004621</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.07278849685069361</v>
+        <v>0.4005060688280094</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-0.1549041894433748</v>
+        <v>0.008175415684418742</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>-90</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1.725633230170963e-31</v>
+        <v>2.933329164887276</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-3.291228071413882</v>
+        <v>0.4339840543235947</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-4.026656205416392e-16</v>
+        <v>3.623318767900233</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2.670618755916465</v>
+        <v>9.242443055210282</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1556609963167663</v>
+        <v>0.7864416251388029</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.89702976502755e-17</v>
+        <v>0.001901201271454379</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-90</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="N10" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1.479114197289397e-31</v>
+        <v>3.070971564483818</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.514269782092496</v>
+        <v>2.092889319742423</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3.288014314184225</v>
+        <v>4.58302808270107</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3.270564711175985e-16</v>
+        <v>9.223278039145931</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.1556609963167663</v>
+        <v>-0.7572814126529369</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1.89702976502755e-17</v>
+        <v>0.0004119686448611116</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>-180</v>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>90</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3.081487911019577e-33</v>
+        <v>3.967498803901822</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.3091629320871749</v>
+        <v>-38.77125130577514</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3.82551112700106e-17</v>
+        <v>-18.48770503512054</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-0.3050188689509281</v>
+        <v>5.99205327411009</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.906297408914157e-17</v>
+        <v>0.07332223507582536</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.1549041894433748</v>
+        <v>0.01750741632722737</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -987,36 +915,30 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="N12" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>-7.113903732080352e-33</v>
+        <v>3.758339881912064</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.0006454467995747181</v>
+        <v>-38.51186721564472</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3.145273147417692e-19</v>
+        <v>-18.08903964391211</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-0.6148272478376777</v>
+        <v>6.585712486827747</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-1.887760986612726e-17</v>
+        <v>-0.07303544917504008</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-0.1549041894433748</v>
+        <v>-0.01519424641070249</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -1031,179 +953,75 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>-90</v>
-      </c>
-      <c r="N13" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row customHeight="1" ht="40" r="14">
-      <c r="A14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Torque 1 max</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Torque 2 max</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Torque 3 max</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Torque 4 max</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Torque 5 max</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Torque 6 max</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="n"/>
+      <c r="H14" s="1" t="n"/>
+      <c r="I14" s="1" t="n"/>
+      <c r="J14" s="1" t="n"/>
+      <c r="K14" s="1" t="n"/>
+      <c r="L14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>0</v>
+        <v>22.60661927447309</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0</v>
+        <v>57.32907156079247</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>34.88092866295083</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>9.330657670349888</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>0.7864416251388029</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Torque 1 max</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Torque 2 max</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Torque 3 max</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Torque 4 max</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Torque 5 max</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Torque 6 max</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Torque 7 max</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>3.944304526105059e-31</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>8.72345184270756</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>3.442918480467286</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>2.825522922199525</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0.1556609963167663</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0.1549041894433748</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
+        <v>0.01750741632722737</v>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
